--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18542,6 +18542,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="791">
+      <c r="A791" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B791" t="n">
+        <v>0</v>
+      </c>
+      <c r="C791" t="n">
+        <v>2</v>
+      </c>
+      <c r="D791" t="n">
+        <v>2</v>
+      </c>
+      <c r="E791" t="n">
+        <v>2</v>
+      </c>
+      <c r="F791" t="n">
+        <v>2</v>
+      </c>
+      <c r="G791" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18565,6 +18565,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="792">
+      <c r="A792" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B792" t="n">
+        <v>0</v>
+      </c>
+      <c r="C792" t="n">
+        <v>2</v>
+      </c>
+      <c r="D792" t="n">
+        <v>2</v>
+      </c>
+      <c r="E792" t="n">
+        <v>2</v>
+      </c>
+      <c r="F792" t="n">
+        <v>2</v>
+      </c>
+      <c r="G792" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18588,6 +18588,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="793">
+      <c r="A793" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B793" t="n">
+        <v>0</v>
+      </c>
+      <c r="C793" t="n">
+        <v>2</v>
+      </c>
+      <c r="D793" t="n">
+        <v>2</v>
+      </c>
+      <c r="E793" t="n">
+        <v>2</v>
+      </c>
+      <c r="F793" t="n">
+        <v>2</v>
+      </c>
+      <c r="G793" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18611,6 +18611,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="794">
+      <c r="A794" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B794" t="n">
+        <v>0</v>
+      </c>
+      <c r="C794" t="n">
+        <v>2</v>
+      </c>
+      <c r="D794" t="n">
+        <v>2</v>
+      </c>
+      <c r="E794" t="n">
+        <v>2</v>
+      </c>
+      <c r="F794" t="n">
+        <v>2</v>
+      </c>
+      <c r="G794" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18475,7 +18475,7 @@
     </row>
     <row r="788">
       <c r="A788" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B788" t="n">
         <v>0</v>
@@ -18498,7 +18498,7 @@
     </row>
     <row r="789">
       <c r="A789" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B789" t="n">
         <v>0</v>
@@ -18521,7 +18521,7 @@
     </row>
     <row r="790">
       <c r="A790" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B790" t="n">
         <v>0</v>
@@ -18544,7 +18544,7 @@
     </row>
     <row r="791">
       <c r="A791" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B791" t="n">
         <v>0</v>
@@ -18567,7 +18567,7 @@
     </row>
     <row r="792">
       <c r="A792" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B792" t="n">
         <v>0</v>
@@ -18590,7 +18590,7 @@
     </row>
     <row r="793">
       <c r="A793" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B793" t="n">
         <v>0</v>
@@ -18613,24 +18613,47 @@
     </row>
     <row r="794">
       <c r="A794" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B794" t="n">
+        <v>0</v>
+      </c>
+      <c r="C794" t="n">
+        <v>2</v>
+      </c>
+      <c r="D794" t="n">
+        <v>2</v>
+      </c>
+      <c r="E794" t="n">
+        <v>2</v>
+      </c>
+      <c r="F794" t="n">
+        <v>2</v>
+      </c>
+      <c r="G794" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="1" t="n">
         <v>46281.2916666667</v>
       </c>
-      <c r="B794" t="n">
-        <v>0</v>
-      </c>
-      <c r="C794" t="n">
-        <v>2</v>
-      </c>
-      <c r="D794" t="n">
-        <v>2</v>
-      </c>
-      <c r="E794" t="n">
-        <v>2</v>
-      </c>
-      <c r="F794" t="n">
-        <v>2</v>
-      </c>
-      <c r="G794" t="s">
+      <c r="B795" t="n">
+        <v>0</v>
+      </c>
+      <c r="C795" t="n">
+        <v>2</v>
+      </c>
+      <c r="D795" t="n">
+        <v>2</v>
+      </c>
+      <c r="E795" t="n">
+        <v>2</v>
+      </c>
+      <c r="F795" t="n">
+        <v>2</v>
+      </c>
+      <c r="G795" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18657,6 +18657,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="796">
+      <c r="A796" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B796" t="n">
+        <v>0</v>
+      </c>
+      <c r="C796" t="n">
+        <v>2</v>
+      </c>
+      <c r="D796" t="n">
+        <v>2</v>
+      </c>
+      <c r="E796" t="n">
+        <v>2</v>
+      </c>
+      <c r="F796" t="n">
+        <v>2</v>
+      </c>
+      <c r="G796" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B797" t="n">
+        <v>0</v>
+      </c>
+      <c r="C797" t="n">
+        <v>2</v>
+      </c>
+      <c r="D797" t="n">
+        <v>2</v>
+      </c>
+      <c r="E797" t="n">
+        <v>2</v>
+      </c>
+      <c r="F797" t="n">
+        <v>2</v>
+      </c>
+      <c r="G797" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18703,6 +18703,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="798">
+      <c r="A798" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B798" t="n">
+        <v>0</v>
+      </c>
+      <c r="C798" t="n">
+        <v>2</v>
+      </c>
+      <c r="D798" t="n">
+        <v>2</v>
+      </c>
+      <c r="E798" t="n">
+        <v>2</v>
+      </c>
+      <c r="F798" t="n">
+        <v>2</v>
+      </c>
+      <c r="G798" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18726,6 +18726,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="799">
+      <c r="A799" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B799" t="n">
+        <v>0</v>
+      </c>
+      <c r="C799" t="n">
+        <v>2</v>
+      </c>
+      <c r="D799" t="n">
+        <v>2</v>
+      </c>
+      <c r="E799" t="n">
+        <v>2</v>
+      </c>
+      <c r="F799" t="n">
+        <v>2</v>
+      </c>
+      <c r="G799" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18749,6 +18749,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="800">
+      <c r="A800" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B800" t="n">
+        <v>0</v>
+      </c>
+      <c r="C800" t="n">
+        <v>2</v>
+      </c>
+      <c r="D800" t="n">
+        <v>2</v>
+      </c>
+      <c r="E800" t="n">
+        <v>2</v>
+      </c>
+      <c r="F800" t="n">
+        <v>2</v>
+      </c>
+      <c r="G800" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18772,6 +18772,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="801">
+      <c r="A801" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B801" t="n">
+        <v>0</v>
+      </c>
+      <c r="C801" t="n">
+        <v>2</v>
+      </c>
+      <c r="D801" t="n">
+        <v>2</v>
+      </c>
+      <c r="E801" t="n">
+        <v>2</v>
+      </c>
+      <c r="F801" t="n">
+        <v>2</v>
+      </c>
+      <c r="G801" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18795,6 +18795,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="802">
+      <c r="A802" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B802" t="n">
+        <v>0</v>
+      </c>
+      <c r="C802" t="n">
+        <v>2</v>
+      </c>
+      <c r="D802" t="n">
+        <v>2</v>
+      </c>
+      <c r="E802" t="n">
+        <v>2</v>
+      </c>
+      <c r="F802" t="n">
+        <v>2</v>
+      </c>
+      <c r="G802" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18818,6 +18818,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="803">
+      <c r="A803" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B803" t="n">
+        <v>0</v>
+      </c>
+      <c r="C803" t="n">
+        <v>2</v>
+      </c>
+      <c r="D803" t="n">
+        <v>2</v>
+      </c>
+      <c r="E803" t="n">
+        <v>2</v>
+      </c>
+      <c r="F803" t="n">
+        <v>2</v>
+      </c>
+      <c r="G803" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18841,6 +18841,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="804">
+      <c r="A804" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B804" t="n">
+        <v>0</v>
+      </c>
+      <c r="C804" t="n">
+        <v>2</v>
+      </c>
+      <c r="D804" t="n">
+        <v>2</v>
+      </c>
+      <c r="E804" t="n">
+        <v>2</v>
+      </c>
+      <c r="F804" t="n">
+        <v>2</v>
+      </c>
+      <c r="G804" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18864,6 +18864,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="805">
+      <c r="A805" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B805" t="n">
+        <v>0</v>
+      </c>
+      <c r="C805" t="n">
+        <v>2</v>
+      </c>
+      <c r="D805" t="n">
+        <v>2</v>
+      </c>
+      <c r="E805" t="n">
+        <v>2</v>
+      </c>
+      <c r="F805" t="n">
+        <v>2</v>
+      </c>
+      <c r="G805" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18887,6 +18887,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="806">
+      <c r="A806" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B806" t="n">
+        <v>0</v>
+      </c>
+      <c r="C806" t="n">
+        <v>2</v>
+      </c>
+      <c r="D806" t="n">
+        <v>2</v>
+      </c>
+      <c r="E806" t="n">
+        <v>2</v>
+      </c>
+      <c r="F806" t="n">
+        <v>2</v>
+      </c>
+      <c r="G806" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18910,6 +18910,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="807">
+      <c r="A807" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B807" t="n">
+        <v>0</v>
+      </c>
+      <c r="C807" t="n">
+        <v>2</v>
+      </c>
+      <c r="D807" t="n">
+        <v>2</v>
+      </c>
+      <c r="E807" t="n">
+        <v>2</v>
+      </c>
+      <c r="F807" t="n">
+        <v>2</v>
+      </c>
+      <c r="G807" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18933,6 +18933,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="808">
+      <c r="A808" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B808" t="n">
+        <v>0</v>
+      </c>
+      <c r="C808" t="n">
+        <v>2</v>
+      </c>
+      <c r="D808" t="n">
+        <v>2</v>
+      </c>
+      <c r="E808" t="n">
+        <v>2</v>
+      </c>
+      <c r="F808" t="n">
+        <v>2</v>
+      </c>
+      <c r="G808" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18956,6 +18956,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="809">
+      <c r="A809" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B809" t="n">
+        <v>0</v>
+      </c>
+      <c r="C809" t="n">
+        <v>2</v>
+      </c>
+      <c r="D809" t="n">
+        <v>2</v>
+      </c>
+      <c r="E809" t="n">
+        <v>2</v>
+      </c>
+      <c r="F809" t="n">
+        <v>2</v>
+      </c>
+      <c r="G809" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -18979,6 +18979,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="810">
+      <c r="A810" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B810" t="n">
+        <v>0</v>
+      </c>
+      <c r="C810" t="n">
+        <v>2</v>
+      </c>
+      <c r="D810" t="n">
+        <v>2</v>
+      </c>
+      <c r="E810" t="n">
+        <v>2</v>
+      </c>
+      <c r="F810" t="n">
+        <v>2</v>
+      </c>
+      <c r="G810" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -19002,6 +19002,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="811">
+      <c r="A811" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B811" t="n">
+        <v>0</v>
+      </c>
+      <c r="C811" t="n">
+        <v>2</v>
+      </c>
+      <c r="D811" t="n">
+        <v>2</v>
+      </c>
+      <c r="E811" t="n">
+        <v>2</v>
+      </c>
+      <c r="F811" t="n">
+        <v>2</v>
+      </c>
+      <c r="G811" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -19048,6 +19048,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="813">
+      <c r="A813" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B813" t="n">
+        <v>0</v>
+      </c>
+      <c r="C813" t="n">
+        <v>2</v>
+      </c>
+      <c r="D813" t="n">
+        <v>2</v>
+      </c>
+      <c r="E813" t="n">
+        <v>2</v>
+      </c>
+      <c r="F813" t="n">
+        <v>2</v>
+      </c>
+      <c r="G813" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -19071,6 +19071,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="814">
+      <c r="A814" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B814" t="n">
+        <v>0</v>
+      </c>
+      <c r="C814" t="n">
+        <v>2</v>
+      </c>
+      <c r="D814" t="n">
+        <v>2</v>
+      </c>
+      <c r="E814" t="n">
+        <v>2</v>
+      </c>
+      <c r="F814" t="n">
+        <v>2</v>
+      </c>
+      <c r="G814" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -19094,6 +19094,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="815">
+      <c r="A815" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B815" t="n">
+        <v>0</v>
+      </c>
+      <c r="C815" t="n">
+        <v>2</v>
+      </c>
+      <c r="D815" t="n">
+        <v>2</v>
+      </c>
+      <c r="E815" t="n">
+        <v>2</v>
+      </c>
+      <c r="F815" t="n">
+        <v>2</v>
+      </c>
+      <c r="G815" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -19117,6 +19117,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="816">
+      <c r="A816" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B816" t="n">
+        <v>0</v>
+      </c>
+      <c r="C816" t="n">
+        <v>2</v>
+      </c>
+      <c r="D816" t="n">
+        <v>2</v>
+      </c>
+      <c r="E816" t="n">
+        <v>2</v>
+      </c>
+      <c r="F816" t="n">
+        <v>2</v>
+      </c>
+      <c r="G816" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -24071,6 +24071,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="818">
+      <c r="A818" t="s">
+        <v>9</v>
+      </c>
+      <c r="B818" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C818" t="n">
+        <v>2</v>
+      </c>
+      <c r="D818" t="n">
+        <v>2</v>
+      </c>
+      <c r="E818" t="n">
+        <v>2</v>
+      </c>
+      <c r="F818" t="n">
+        <v>2</v>
+      </c>
+      <c r="G818" t="n">
+        <v>2</v>
+      </c>
+      <c r="H818" t="n">
+        <v>0</v>
+      </c>
+      <c r="I818" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -24100,6 +24100,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="819">
+      <c r="A819" t="s">
+        <v>9</v>
+      </c>
+      <c r="B819" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C819" t="n">
+        <v>2</v>
+      </c>
+      <c r="D819" t="n">
+        <v>2</v>
+      </c>
+      <c r="E819" t="n">
+        <v>2</v>
+      </c>
+      <c r="F819" t="n">
+        <v>2</v>
+      </c>
+      <c r="G819" t="n">
+        <v>2</v>
+      </c>
+      <c r="H819" t="n">
+        <v>0</v>
+      </c>
+      <c r="I819" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -24129,6 +24129,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="820">
+      <c r="A820" t="s">
+        <v>9</v>
+      </c>
+      <c r="B820" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C820" t="n">
+        <v>2</v>
+      </c>
+      <c r="D820" t="n">
+        <v>2</v>
+      </c>
+      <c r="E820" t="n">
+        <v>2</v>
+      </c>
+      <c r="F820" t="n">
+        <v>2</v>
+      </c>
+      <c r="G820" t="n">
+        <v>2</v>
+      </c>
+      <c r="H820" t="n">
+        <v>0</v>
+      </c>
+      <c r="I820" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -24158,6 +24158,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="821">
+      <c r="A821" t="s">
+        <v>9</v>
+      </c>
+      <c r="B821" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C821" t="n">
+        <v>2</v>
+      </c>
+      <c r="D821" t="n">
+        <v>2</v>
+      </c>
+      <c r="E821" t="n">
+        <v>2</v>
+      </c>
+      <c r="F821" t="n">
+        <v>2</v>
+      </c>
+      <c r="G821" t="n">
+        <v>2</v>
+      </c>
+      <c r="H821" t="n">
+        <v>0</v>
+      </c>
+      <c r="I821" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -24187,6 +24187,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="822">
+      <c r="A822" t="s">
+        <v>9</v>
+      </c>
+      <c r="B822" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C822" t="n">
+        <v>2</v>
+      </c>
+      <c r="D822" t="n">
+        <v>2</v>
+      </c>
+      <c r="E822" t="n">
+        <v>2</v>
+      </c>
+      <c r="F822" t="n">
+        <v>2</v>
+      </c>
+      <c r="G822" t="n">
+        <v>2</v>
+      </c>
+      <c r="H822" t="n">
+        <v>0</v>
+      </c>
+      <c r="I822" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -24216,6 +24216,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="823">
+      <c r="A823" t="s">
+        <v>9</v>
+      </c>
+      <c r="B823" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C823" t="n">
+        <v>2</v>
+      </c>
+      <c r="D823" t="n">
+        <v>2</v>
+      </c>
+      <c r="E823" t="n">
+        <v>2</v>
+      </c>
+      <c r="F823" t="n">
+        <v>2</v>
+      </c>
+      <c r="G823" t="n">
+        <v>2</v>
+      </c>
+      <c r="H823" t="n">
+        <v>0</v>
+      </c>
+      <c r="I823" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -24245,6 +24245,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="824">
+      <c r="A824" t="s">
+        <v>9</v>
+      </c>
+      <c r="B824" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C824" t="n">
+        <v>2</v>
+      </c>
+      <c r="D824" t="n">
+        <v>2</v>
+      </c>
+      <c r="E824" t="n">
+        <v>2</v>
+      </c>
+      <c r="F824" t="n">
+        <v>2</v>
+      </c>
+      <c r="G824" t="n">
+        <v>2</v>
+      </c>
+      <c r="H824" t="n">
+        <v>0</v>
+      </c>
+      <c r="I824" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -24274,6 +24274,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="825">
+      <c r="A825" t="s">
+        <v>9</v>
+      </c>
+      <c r="B825" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C825" t="n">
+        <v>2</v>
+      </c>
+      <c r="D825" t="n">
+        <v>2</v>
+      </c>
+      <c r="E825" t="n">
+        <v>2</v>
+      </c>
+      <c r="F825" t="n">
+        <v>2</v>
+      </c>
+      <c r="G825" t="n">
+        <v>2</v>
+      </c>
+      <c r="H825" t="n">
+        <v>0</v>
+      </c>
+      <c r="I825" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RMT.MI.xlsx
+++ b/data/RMT.MI.xlsx
@@ -24303,6 +24303,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="826">
+      <c r="A826" t="s">
+        <v>9</v>
+      </c>
+      <c r="B826" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C826" t="n">
+        <v>2</v>
+      </c>
+      <c r="D826" t="n">
+        <v>2</v>
+      </c>
+      <c r="E826" t="n">
+        <v>2</v>
+      </c>
+      <c r="F826" t="n">
+        <v>2</v>
+      </c>
+      <c r="G826" t="n">
+        <v>2</v>
+      </c>
+      <c r="H826" t="n">
+        <v>0</v>
+      </c>
+      <c r="I826" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
